--- a/data/processed/HazardFactors.xlsx
+++ b/data/processed/HazardFactors.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adi/Desktop/CareerPlan/Gov Applications/Current Active Applications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adi/Desktop/Projects/KC_BA_POC/KC_CrimeAnalytics/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DB124A-49F8-3743-946F-3418DF459000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E8DF97-54BC-B64F-8823-E25D26449053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{78CD55C8-3C93-1E4E-8F33-DD6DB4FB15A1}"/>
+    <workbookView xWindow="-18800" yWindow="2120" windowWidth="17960" windowHeight="16940" xr2:uid="{78CD55C8-3C93-1E4E-8F33-DD6DB4FB15A1}"/>
   </bookViews>
   <sheets>
     <sheet name="HazardFactors" sheetId="1" r:id="rId1"/>
@@ -41,15 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
-    <t>Code / Element</t>
-  </si>
-  <si>
-    <t>Label / Description</t>
-  </si>
-  <si>
-    <t>Notes / Rules</t>
-  </si>
-  <si>
     <t>*</t>
   </si>
   <si>
@@ -123,6 +114,15 @@
   </si>
   <si>
     <t>DOMESTIC VIOLENCE</t>
+  </si>
+  <si>
+    <t>HazardCode</t>
+  </si>
+  <si>
+    <t>HazardCodeDesc</t>
+  </si>
+  <si>
+    <t>HazardCodeNotes</t>
   </si>
 </sst>
 </file>
@@ -520,30 +520,30 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" style="3" customWidth="1"/>
-    <col min="2" max="2" width="61.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="102" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -562,10 +562,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -573,10 +573,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -584,10 +584,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -606,10 +606,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -617,10 +617,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -628,10 +628,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -639,10 +639,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -650,10 +650,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
